--- a/artfynd/A 54073-2021 artfynd.xlsx
+++ b/artfynd/A 54073-2021 artfynd.xlsx
@@ -774,7 +774,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mikael Andersson, Per Karlsson Linderum</t>
+          <t>Per Karlsson Linderum, Mikael Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -788,7 +788,7 @@
         <v>123428514</v>
       </c>
       <c r="B3" t="n">
-        <v>92266</v>
+        <v>92272</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mikael Andersson, Per Karlsson Linderum</t>
+          <t>Per Karlsson Linderum, Mikael Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 54073-2021 artfynd.xlsx
+++ b/artfynd/A 54073-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123428547</v>
+        <v>123428514</v>
       </c>
       <c r="B2" t="n">
-        <v>57497</v>
+        <v>92292</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>386557</v>
+        <v>386626</v>
       </c>
       <c r="R2" t="n">
-        <v>6584741</v>
+        <v>6584831</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123428514</v>
+        <v>123428547</v>
       </c>
       <c r="B3" t="n">
-        <v>92275</v>
+        <v>57503</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,21 +801,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5449</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>386626</v>
+        <v>386557</v>
       </c>
       <c r="R3" t="n">
-        <v>6584831</v>
+        <v>6584741</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 54073-2021 artfynd.xlsx
+++ b/artfynd/A 54073-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123428514</v>
+        <v>123428547</v>
       </c>
       <c r="B2" t="n">
-        <v>92292</v>
+        <v>57506</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5449</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>386626</v>
+        <v>386557</v>
       </c>
       <c r="R2" t="n">
-        <v>6584831</v>
+        <v>6584741</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123428547</v>
+        <v>123428514</v>
       </c>
       <c r="B3" t="n">
-        <v>57503</v>
+        <v>92297</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,21 +801,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5449</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>386557</v>
+        <v>386626</v>
       </c>
       <c r="R3" t="n">
-        <v>6584741</v>
+        <v>6584831</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 54073-2021 artfynd.xlsx
+++ b/artfynd/A 54073-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123428547</v>
+        <v>123428514</v>
       </c>
       <c r="B2" t="n">
-        <v>57506</v>
+        <v>92299</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>386557</v>
+        <v>386626</v>
       </c>
       <c r="R2" t="n">
-        <v>6584741</v>
+        <v>6584831</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123428514</v>
+        <v>123428547</v>
       </c>
       <c r="B3" t="n">
-        <v>92297</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,21 +801,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5449</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>386626</v>
+        <v>386557</v>
       </c>
       <c r="R3" t="n">
-        <v>6584831</v>
+        <v>6584741</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 54073-2021 artfynd.xlsx
+++ b/artfynd/A 54073-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123428514</v>
+        <v>123428547</v>
       </c>
       <c r="B2" t="n">
-        <v>92299</v>
+        <v>57507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5449</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>386626</v>
+        <v>386557</v>
       </c>
       <c r="R2" t="n">
-        <v>6584831</v>
+        <v>6584741</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123428547</v>
+        <v>123428514</v>
       </c>
       <c r="B3" t="n">
-        <v>57507</v>
+        <v>92299</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,21 +801,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5449</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>386557</v>
+        <v>386626</v>
       </c>
       <c r="R3" t="n">
-        <v>6584741</v>
+        <v>6584831</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 54073-2021 artfynd.xlsx
+++ b/artfynd/A 54073-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>123428547</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -778,116 +773,6 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
-        <is>
-          <t>NVI Grums-Lång</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>123428514</v>
-      </c>
-      <c r="B3" t="n">
-        <v>92321</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>5449</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Svart taggsvamp</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Phellodon niger</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Grums-Lång, Vrm</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>386626</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6584831</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Grums</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Borgvik</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Mikael Andersson</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Mikael Andersson, Per Karlsson Linderum</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
         <is>
           <t>NVI Grums-Lång</t>
         </is>

--- a/artfynd/A 54073-2021 artfynd.xlsx
+++ b/artfynd/A 54073-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,8 +782,16 @@
           <t>NVI Grums-Lång</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123428547</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>